--- a/data/ct_scoop/ct_scoop_links_2026-05-27.xlsx
+++ b/data/ct_scoop/ct_scoop_links_2026-05-27.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,88 +440,148 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SOUTHBURY SCOOP: Blue Fig Garden sets opening date in Southbury!</t>
+          <t>MANCHESTER SCOOP: Carlito's Bakery to close this fall</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/southbury-scoop-blue-fig-garden-sets-opening-date-in-southbury</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/manchester-scoop-carlitos-bakery-to-close-this-fall</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MANCHESTER SCOOP: Dollar Tree starts construction on new store!</t>
+          <t>SOUTH WINDSOR SCOOP: Dairy Queen building &amp; mini-golf/batting cage facility listed for sale!</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/manchester-scoop-dollar-tree-starts-construction-on-new-store</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/south-windsor-scoop-dairy-queen-building-mini-golfbatting-cage-facility-listed-for-sale</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GRANBY SCOOP: New cat cafe coming soon to Granby</t>
+          <t>CHESHIRE SCOOP: New tenants open at The Shops at Stone Bridge</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/granby-scoop-new-cat-cafe-coming-soon-to-granby</t>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/cheshire-scoop-new-tenants-open-at-the-shops-at-stone-bridge</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NEWINGTON SCOOP: Arby's closes Berlin Turnpike location</t>
+          <t>WESTPORT SCOOP: Frank Pepe Pizzeria Napoletana opening on June 1st!</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/newington-scoop-arbys-closes-berlin-turnpike-location</t>
+          <t>https://www.theconnecticutscoop.com/all-fairfield-county-posts/westport-scoop-frank-pepe-pizzeria-napoletana-opening-on-june-1st</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NORTH HAVEN SCOOP: Josephys on Whitney by Chef Mickey opens!</t>
+          <t>SOUTHBURY SCOOP: Blue Fig Garden sets opening date in Southbury!</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/north-haven-scoop-josephys-on-whitney-by-chef-mickey-opens</t>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/southbury-scoop-blue-fig-garden-sets-opening-date-in-southbury</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NEW HAVEN SCOOP: Muzi's Munchies opens in New Haven</t>
+          <t>MANCHESTER SCOOP: Dollar Tree starts construction on new store!</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
         <v>46167</v>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/manchester-scoop-dollar-tree-starts-construction-on-new-store</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GRANBY SCOOP: New cat cafe coming soon to Granby</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/granby-scoop-new-cat-cafe-coming-soon-to-granby</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NEWINGTON SCOOP: Arby's closes Berlin Turnpike location</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/newington-scoop-arbys-closes-berlin-turnpike-location</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NORTH HAVEN SCOOP: Josephys on Whitney by Chef Mickey opens!</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/north-haven-scoop-josephys-on-whitney-by-chef-mickey-opens</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NEW HAVEN SCOOP: Muzi's Munchies opens in New Haven</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/new-haven-scoop-muzis-munchies-opens-in-new-haven</t>
         </is>
